--- a/output/upload/S00022_2242_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00022_2242_경영인H정기보험_무배당.xlsx
@@ -1372,11 +1372,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2242A01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형 표준체</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22421</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형 표준체</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00022_2242_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00022_2242_경영인H정기보험_무배당.xlsx
@@ -1384,7 +1384,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>2242001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">

--- a/output/upload/S00022_2242_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00022_2242_경영인H정기보험_무배당.xlsx
@@ -1436,13 +1436,41 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2242A02</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형 건강체</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2242002</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형 건강체</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
@@ -1452,7 +1480,11 @@
       <c r="O8" s="6" t="n"/>
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="6" t="n"/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S8" s="6" t="n"/>
       <c r="T8" s="6" t="n"/>
       <c r="U8" s="6" t="n"/>
@@ -1468,13 +1500,41 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2242A03</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형 표준체</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>2242003</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형 표준체</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="6" t="n"/>
@@ -1484,7 +1544,11 @@
       <c r="O9" s="6" t="n"/>
       <c r="P9" s="6" t="n"/>
       <c r="Q9" s="6" t="n"/>
-      <c r="R9" s="6" t="n"/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S9" s="6" t="n"/>
       <c r="T9" s="6" t="n"/>
       <c r="U9" s="6" t="n"/>
@@ -1500,13 +1564,41 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2242A04</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형 건강체</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>2242004</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형 건강체</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
@@ -1516,7 +1608,11 @@
       <c r="O10" s="6" t="n"/>
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
-      <c r="R10" s="6" t="n"/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S10" s="6" t="n"/>
       <c r="T10" s="6" t="n"/>
       <c r="U10" s="6" t="n"/>

--- a/output/upload/S00022_2242_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00022_2242_경영인H정기보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1407,15 +1407,47 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
@@ -1471,15 +1503,47 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="6" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
@@ -1535,15 +1599,47 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
-      <c r="O9" s="6" t="n"/>
-      <c r="P9" s="6" t="n"/>
-      <c r="Q9" s="6" t="n"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
@@ -1599,15 +1695,47 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="6" t="n"/>
-      <c r="Q10" s="6" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
